--- a/對應表.xlsx
+++ b/對應表.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\catmario\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/easn/code/catmario/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9DEC9D0-AFB6-44D0-9C6F-F4C8C34D2D8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2572B412-196C-9840-A3AB-D3709DE2C5C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11295" xr2:uid="{8D3ADF05-6E10-4DC5-8529-E0F0A0AD7E8F}"/>
+    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11300" xr2:uid="{8D3ADF05-6E10-4DC5-8529-E0F0A0AD7E8F}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -118,7 +118,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>編號</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -157,6 +157,10 @@
   </si>
   <si>
     <t>longtube</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>隱形box</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -164,7 +168,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -647,15 +651,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06C0AE9F-6DB3-40DA-B2EC-F82B368A21F6}">
   <dimension ref="A1:C20"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="5.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="8.1640625" style="1" customWidth="1"/>
     <col min="4" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -663,7 +667,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -671,7 +675,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="35" customHeight="1">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -682,7 +686,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="35" customHeight="1">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -693,7 +697,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="35" customHeight="1">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -704,7 +708,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="35" customHeight="1">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -715,7 +719,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="35" customHeight="1">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -726,7 +730,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" ht="35" customHeight="1">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -737,7 +741,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="35" customHeight="1">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -748,17 +752,24 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="35.1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="1:3" ht="35.1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12" spans="1:3" ht="35.1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="1:3" ht="35.1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="1:3" ht="35.1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15" spans="1:3" ht="35.1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16" spans="1:3" ht="35.1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17" ht="35.1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="18" ht="35.1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="19" ht="35.1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="20" ht="35.1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="1:3" ht="35" customHeight="1">
+      <c r="A10" s="1">
+        <v>8</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="35" customHeight="1"/>
+    <row r="12" spans="1:3" ht="35" customHeight="1"/>
+    <row r="13" spans="1:3" ht="35" customHeight="1"/>
+    <row r="14" spans="1:3" ht="35" customHeight="1"/>
+    <row r="15" spans="1:3" ht="35" customHeight="1"/>
+    <row r="16" spans="1:3" ht="35" customHeight="1"/>
+    <row r="17" ht="35" customHeight="1"/>
+    <row r="18" ht="35" customHeight="1"/>
+    <row r="19" ht="35" customHeight="1"/>
+    <row r="20" ht="35" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/對應表.xlsx
+++ b/對應表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/easn/code/catmario/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2572B412-196C-9840-A3AB-D3709DE2C5C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2EA6B1A-36E6-D14A-BC6C-E73945FF2F09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11300" xr2:uid="{8D3ADF05-6E10-4DC5-8529-E0F0A0AD7E8F}"/>
   </bookViews>
@@ -118,7 +118,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>編號</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -144,10 +144,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>box</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>brock4</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -161,6 +157,26 @@
   </si>
   <si>
     <t>隱形box</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>upbox</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>coin</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>coinbox</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>monstr3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>monsterbox</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -650,16 +666,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06C0AE9F-6DB3-40DA-B2EC-F82B368A21F6}">
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8.1640625" style="1" customWidth="1"/>
-    <col min="4" max="16384" width="9" style="1"/>
+    <col min="4" max="4" width="15.5" style="1" customWidth="1"/>
+    <col min="5" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -667,7 +684,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:4">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -675,7 +692,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="35" customHeight="1">
+    <row r="3" spans="1:4" ht="35" customHeight="1">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -686,7 +703,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="35" customHeight="1">
+    <row r="4" spans="1:4" ht="35" customHeight="1">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -697,7 +714,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="35" customHeight="1">
+    <row r="5" spans="1:4" ht="35" customHeight="1">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -708,64 +725,90 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="35" customHeight="1">
+    <row r="6" spans="1:4" ht="35" customHeight="1">
       <c r="A6" s="1">
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C6" s="1" t="e" vm="4">
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" ht="35" customHeight="1">
+      <c r="D6" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="35" customHeight="1">
       <c r="A7" s="1">
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C7" s="1" t="e" vm="5">
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="35" customHeight="1">
+    <row r="8" spans="1:4" ht="35" customHeight="1">
       <c r="A8" s="1">
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C8" s="1" t="e" vm="6">
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="35" customHeight="1">
+    <row r="9" spans="1:4" ht="35" customHeight="1">
       <c r="A9" s="1">
         <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C9" s="1" t="e" vm="7">
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="35" customHeight="1">
+    <row r="10" spans="1:4" ht="35" customHeight="1">
       <c r="A10" s="1">
         <v>8</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="35" customHeight="1">
+      <c r="A11" s="1">
+        <v>9</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="1" t="e" vm="4">
+        <v>#VALUE!</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="35" customHeight="1">
+      <c r="A12" s="1">
         <v>10</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" ht="35" customHeight="1"/>
-    <row r="12" spans="1:3" ht="35" customHeight="1"/>
-    <row r="13" spans="1:3" ht="35" customHeight="1"/>
-    <row r="14" spans="1:3" ht="35" customHeight="1"/>
-    <row r="15" spans="1:3" ht="35" customHeight="1"/>
-    <row r="16" spans="1:3" ht="35" customHeight="1"/>
+      <c r="B12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="1" t="e" vm="4">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="35" customHeight="1"/>
+    <row r="14" spans="1:4" ht="35" customHeight="1"/>
+    <row r="15" spans="1:4" ht="35" customHeight="1"/>
+    <row r="16" spans="1:4" ht="35" customHeight="1"/>
     <row r="17" ht="35" customHeight="1"/>
     <row r="18" ht="35" customHeight="1"/>
     <row r="19" ht="35" customHeight="1"/>

--- a/對應表.xlsx
+++ b/對應表.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/easn/code/catmario/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\catmario\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2572B412-196C-9840-A3AB-D3709DE2C5C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59C24D97-C43E-4C6C-AA3C-FDDAFF2C0393}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11300" xr2:uid="{8D3ADF05-6E10-4DC5-8529-E0F0A0AD7E8F}"/>
+    <workbookView minimized="1" xWindow="3210" yWindow="1455" windowWidth="21600" windowHeight="11295" xr2:uid="{8D3ADF05-6E10-4DC5-8529-E0F0A0AD7E8F}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
   <metadataTypes count="1">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="7">
+  <futureMetadata name="XLRICHVALUE" count="8">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -90,8 +90,15 @@
         </ext>
       </extLst>
     </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="7"/>
+        </ext>
+      </extLst>
+    </bk>
   </futureMetadata>
-  <valueMetadata count="7">
+  <valueMetadata count="8">
     <bk>
       <rc t="1" v="0"/>
     </bk>
@@ -112,13 +119,16 @@
     </bk>
     <bk>
       <rc t="1" v="6"/>
+    </bk>
+    <bk>
+      <rc t="1" v="7"/>
     </bk>
   </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>編號</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -161,6 +171,10 @@
   </si>
   <si>
     <t>隱形box</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>longtube_rotate90</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -168,7 +182,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -280,7 +294,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="7">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="8">
   <rv s="0">
     <v>0</v>
     <v>5</v>
@@ -309,6 +323,10 @@
     <v>6</v>
     <v>5</v>
   </rv>
+  <rv s="0">
+    <v>7</v>
+    <v>5</v>
+  </rv>
 </rvData>
 </file>
 
@@ -330,6 +348,7 @@
   <rel r:id="rId5"/>
   <rel r:id="rId6"/>
   <rel r:id="rId7"/>
+  <rel r:id="rId8"/>
 </richValueRels>
 </file>
 
@@ -651,15 +670,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06C0AE9F-6DB3-40DA-B2EC-F82B368A21F6}">
   <dimension ref="A1:C20"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.1640625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="5.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.125" style="1" customWidth="1"/>
     <col min="4" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -667,7 +686,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -675,7 +694,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="35" customHeight="1">
+    <row r="3" spans="1:3" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -686,7 +705,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="35" customHeight="1">
+    <row r="4" spans="1:3" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -697,7 +716,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="35" customHeight="1">
+    <row r="5" spans="1:3" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -708,7 +727,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="35" customHeight="1">
+    <row r="6" spans="1:3" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -719,7 +738,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="35" customHeight="1">
+    <row r="7" spans="1:3" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -730,7 +749,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="35" customHeight="1">
+    <row r="8" spans="1:3" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -741,7 +760,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="35" customHeight="1">
+    <row r="9" spans="1:3" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -752,7 +771,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="35" customHeight="1">
+    <row r="10" spans="1:3" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -760,16 +779,26 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="35" customHeight="1"/>
-    <row r="12" spans="1:3" ht="35" customHeight="1"/>
-    <row r="13" spans="1:3" ht="35" customHeight="1"/>
-    <row r="14" spans="1:3" ht="35" customHeight="1"/>
-    <row r="15" spans="1:3" ht="35" customHeight="1"/>
-    <row r="16" spans="1:3" ht="35" customHeight="1"/>
-    <row r="17" ht="35" customHeight="1"/>
-    <row r="18" ht="35" customHeight="1"/>
-    <row r="19" ht="35" customHeight="1"/>
-    <row r="20" ht="35" customHeight="1"/>
+    <row r="11" spans="1:3" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>9</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="1" t="e" vm="8">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="35.1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:3" ht="35.1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:3" ht="35.1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="1:3" ht="35.1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="1:3" ht="35.1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17" ht="35.1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="18" ht="35.1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="19" ht="35.1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="20" ht="35.1" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/對應表.xlsx
+++ b/對應表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\catmario\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59C24D97-C43E-4C6C-AA3C-FDDAFF2C0393}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E131459-7B01-48F5-9471-C804D6F40341}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="3210" yWindow="1455" windowWidth="21600" windowHeight="11295" xr2:uid="{8D3ADF05-6E10-4DC5-8529-E0F0A0AD7E8F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8D3ADF05-6E10-4DC5-8529-E0F0A0AD7E8F}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
   <metadataTypes count="1">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="8">
+  <futureMetadata name="XLRICHVALUE" count="11">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -97,8 +97,29 @@
         </ext>
       </extLst>
     </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="8"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="9"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="10"/>
+        </ext>
+      </extLst>
+    </bk>
   </futureMetadata>
-  <valueMetadata count="8">
+  <valueMetadata count="11">
     <bk>
       <rc t="1" v="0"/>
     </bk>
@@ -122,13 +143,22 @@
     </bk>
     <bk>
       <rc t="1" v="7"/>
+    </bk>
+    <bk>
+      <rc t="1" v="8"/>
+    </bk>
+    <bk>
+      <rc t="1" v="9"/>
+    </bk>
+    <bk>
+      <rc t="1" v="10"/>
     </bk>
   </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>編號</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -154,10 +184,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>box</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>brock4</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -176,13 +202,143 @@
   <si>
     <t>longtube_rotate90</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>box(移動</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Gen Jyuu Gothic Bold"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>box(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>饅頭盒</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Gen Jyuu Gothic Bold"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>box(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>星星盒</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Gen Jyuu Gothic Bold"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>box(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>金幣盒</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Gen Jyuu Gothic Bold"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>brock7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>隱形box(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>金幣</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Gen Jyuu Gothic Bold"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>flag</t>
+  </si>
+  <si>
+    <t>castle</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -205,6 +361,20 @@
       <name val="Gen Jyuu Gothic Bold"/>
       <family val="2"/>
       <charset val="136"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Microsoft JhengHei"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Gen Jyuu Gothic Bold"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -294,7 +464,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="8">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="11">
   <rv s="0">
     <v>0</v>
     <v>5</v>
@@ -325,6 +495,18 @@
   </rv>
   <rv s="0">
     <v>7</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>8</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>9</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>10</v>
     <v>5</v>
   </rv>
 </rvData>
@@ -349,6 +531,9 @@
   <rel r:id="rId6"/>
   <rel r:id="rId7"/>
   <rel r:id="rId8"/>
+  <rel r:id="rId9"/>
+  <rel r:id="rId10"/>
+  <rel r:id="rId11"/>
 </richValueRels>
 </file>
 
@@ -669,8 +854,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06C0AE9F-6DB3-40DA-B2EC-F82B368A21F6}">
-  <dimension ref="A1:C20"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C21"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="5.625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="21.25" style="1" bestFit="1" customWidth="1"/>
@@ -678,7 +863,7 @@
     <col min="4" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -686,7 +871,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -694,7 +879,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="35.1" customHeight="1">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -705,7 +890,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="35.1" customHeight="1">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -716,7 +901,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="35.1" customHeight="1">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -727,78 +912,146 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="35.1" customHeight="1">
       <c r="A6" s="1">
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C6" s="1" t="e" vm="4">
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="35.1" customHeight="1">
       <c r="A7" s="1">
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C7" s="1" t="e" vm="5">
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" ht="35.1" customHeight="1">
       <c r="A8" s="1">
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C8" s="1" t="e" vm="6">
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="35.1" customHeight="1">
       <c r="A9" s="1">
         <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C9" s="1" t="e" vm="7">
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="35.1" customHeight="1">
       <c r="A10" s="1">
         <v>8</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="35.1" customHeight="1">
       <c r="A11" s="1">
         <v>9</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="1" t="e" vm="8">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="35.1" customHeight="1">
+      <c r="A12" s="1">
+        <v>10</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="1" t="e" vm="8">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="35.1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="1:3" ht="35.1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="1:3" ht="35.1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15" spans="1:3" ht="35.1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16" spans="1:3" ht="35.1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17" ht="35.1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="18" ht="35.1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="19" ht="35.1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="20" ht="35.1" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="C12" s="1" t="e" vm="4">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="35.1" customHeight="1">
+      <c r="A13" s="1">
+        <v>11</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" s="1" t="e" vm="4">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="35.1" customHeight="1">
+      <c r="A14" s="1">
+        <v>12</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" s="1" t="e" vm="4">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="35.1" customHeight="1">
+      <c r="A15" s="1">
+        <v>13</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="1" t="e" vm="9">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="35.1" customHeight="1">
+      <c r="A16" s="1">
+        <v>14</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C16" s="1" t="e" vm="10">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="35.1" customHeight="1">
+      <c r="A17" s="1">
+        <v>15</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="35.1" customHeight="1">
+      <c r="A18" s="1">
+        <v>16</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" s="1" t="e" vm="11">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="35.1" customHeight="1"/>
+    <row r="20" spans="1:3" ht="35.1" customHeight="1"/>
+    <row r="21" spans="1:3" ht="35.1" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/對應表.xlsx
+++ b/對應表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\catmario\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E131459-7B01-48F5-9471-C804D6F40341}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0476D0CA-A14D-4CC1-A513-097E3A7DB58D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8D3ADF05-6E10-4DC5-8529-E0F0A0AD7E8F}"/>
   </bookViews>
@@ -16,6 +16,7 @@
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -158,7 +159,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>編號</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -328,17 +329,50 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>castle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>flag</t>
-  </si>
-  <si>
-    <t>castle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>隱形box(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>紫色菇菇</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Gen Jyuu Gothic Bold"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -375,6 +409,14 @@
       <color theme="1"/>
       <name val="Gen Jyuu Gothic Bold"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Microsoft JhengHei"/>
+      <family val="2"/>
+      <charset val="136"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1013,7 +1055,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C15" s="1" t="e" vm="9">
         <v>#VALUE!</v>
@@ -1043,13 +1085,23 @@
         <v>16</v>
       </c>
       <c r="B18" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="1" t="e" vm="11">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="35.1" customHeight="1">
+      <c r="A19" s="1">
         <v>17</v>
       </c>
-      <c r="C18" s="1" t="e" vm="11">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="35.1" customHeight="1"/>
+      <c r="B19" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
     <row r="20" spans="1:3" ht="35.1" customHeight="1"/>
     <row r="21" spans="1:3" ht="35.1" customHeight="1"/>
   </sheetData>

--- a/對應表.xlsx
+++ b/對應表.xlsx
@@ -1,22 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10402"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\catmario\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/easn/code/catmario/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0476D0CA-A14D-4CC1-A513-097E3A7DB58D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7D1DEF6-8FEB-2E48-B636-5CB8BBB9B099}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8D3ADF05-6E10-4DC5-8529-E0F0A0AD7E8F}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29040" windowHeight="15720" xr2:uid="{8D3ADF05-6E10-4DC5-8529-E0F0A0AD7E8F}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -159,7 +158,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>編號</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -365,6 +364,14 @@
   </si>
   <si>
     <t xml:space="preserve"> </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>drop brock10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>drop brock13</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -897,11 +904,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06C0AE9F-6DB3-40DA-B2EC-F82B368A21F6}">
   <dimension ref="A1:C21"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="5.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.1640625" style="1" customWidth="1"/>
     <col min="4" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -921,7 +928,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="35.1" customHeight="1">
+    <row r="3" spans="1:3" ht="35" customHeight="1">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -932,7 +939,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="35.1" customHeight="1">
+    <row r="4" spans="1:3" ht="35" customHeight="1">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -943,7 +950,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="35.1" customHeight="1">
+    <row r="5" spans="1:3" ht="35" customHeight="1">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -954,7 +961,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="35.1" customHeight="1">
+    <row r="6" spans="1:3" ht="35" customHeight="1">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -965,7 +972,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="35.1" customHeight="1">
+    <row r="7" spans="1:3" ht="35" customHeight="1">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -976,7 +983,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="35.1" customHeight="1">
+    <row r="8" spans="1:3" ht="35" customHeight="1">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -987,7 +994,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="35.1" customHeight="1">
+    <row r="9" spans="1:3" ht="35" customHeight="1">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -998,7 +1005,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="35.1" customHeight="1">
+    <row r="10" spans="1:3" ht="35" customHeight="1">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -1006,7 +1013,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="35.1" customHeight="1">
+    <row r="11" spans="1:3" ht="35" customHeight="1">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -1017,7 +1024,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="35.1" customHeight="1">
+    <row r="12" spans="1:3" ht="35" customHeight="1">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -1028,18 +1035,18 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="35.1" customHeight="1">
+    <row r="13" spans="1:3" ht="35" customHeight="1">
       <c r="A13" s="1">
         <v>11</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C13" s="1" t="e" vm="4">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="35.1" customHeight="1">
+      <c r="C13" s="1" t="e" vm="3">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="35" customHeight="1">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -1050,7 +1057,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="35.1" customHeight="1">
+    <row r="15" spans="1:3" ht="35" customHeight="1">
       <c r="A15" s="1">
         <v>13</v>
       </c>
@@ -1061,7 +1068,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="35.1" customHeight="1">
+    <row r="16" spans="1:3" ht="35" customHeight="1">
       <c r="A16" s="1">
         <v>14</v>
       </c>
@@ -1072,7 +1079,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="35.1" customHeight="1">
+    <row r="17" spans="1:3" ht="35" customHeight="1">
       <c r="A17" s="1">
         <v>15</v>
       </c>
@@ -1080,7 +1087,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="35.1" customHeight="1">
+    <row r="18" spans="1:3" ht="35" customHeight="1">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -1091,7 +1098,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="35.1" customHeight="1">
+    <row r="19" spans="1:3" ht="35" customHeight="1">
       <c r="A19" s="1">
         <v>17</v>
       </c>
@@ -1102,8 +1109,28 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="35.1" customHeight="1"/>
-    <row r="21" spans="1:3" ht="35.1" customHeight="1"/>
+    <row r="20" spans="1:3" ht="35" customHeight="1">
+      <c r="A20" s="1">
+        <v>18</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C20" s="1" t="e" vm="1">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="35" customHeight="1">
+      <c r="A21" s="1">
+        <v>19</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C21" s="1" t="e" vm="2">
+        <v>#VALUE!</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/對應表.xlsx
+++ b/對應表.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10402"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/easn/code/catmario/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\catmario\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7D1DEF6-8FEB-2E48-B636-5CB8BBB9B099}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6F8FBE5-A957-40DE-A0AE-5B22499D04ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29040" windowHeight="15720" xr2:uid="{8D3ADF05-6E10-4DC5-8529-E0F0A0AD7E8F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{8D3ADF05-6E10-4DC5-8529-E0F0A0AD7E8F}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
   <metadataTypes count="1">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="11">
+  <futureMetadata name="XLRICHVALUE" count="12">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -118,8 +118,15 @@
         </ext>
       </extLst>
     </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="11"/>
+        </ext>
+      </extLst>
+    </bk>
   </futureMetadata>
-  <valueMetadata count="11">
+  <valueMetadata count="12">
     <bk>
       <rc t="1" v="0"/>
     </bk>
@@ -152,13 +159,16 @@
     </bk>
     <bk>
       <rc t="1" v="10"/>
+    </bk>
+    <bk>
+      <rc t="1" v="11"/>
     </bk>
   </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>編號</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -372,6 +382,14 @@
   </si>
   <si>
     <t>drop brock13</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stupid clode</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -513,7 +531,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="11">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="12">
   <rv s="0">
     <v>0</v>
     <v>5</v>
@@ -556,6 +574,10 @@
   </rv>
   <rv s="0">
     <v>10</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>11</v>
     <v>5</v>
   </rv>
 </rvData>
@@ -583,6 +605,7 @@
   <rel r:id="rId9"/>
   <rel r:id="rId10"/>
   <rel r:id="rId11"/>
+  <rel r:id="rId12"/>
 </richValueRels>
 </file>
 
@@ -903,12 +926,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06C0AE9F-6DB3-40DA-B2EC-F82B368A21F6}">
-  <dimension ref="A1:C21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
+  <dimension ref="A1:C22"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.1640625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="5.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.125" style="1" customWidth="1"/>
     <col min="4" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -928,7 +951,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="35" customHeight="1">
+    <row r="3" spans="1:3" ht="35.1" customHeight="1">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -939,7 +962,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="35" customHeight="1">
+    <row r="4" spans="1:3" ht="35.1" customHeight="1">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -950,7 +973,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="35" customHeight="1">
+    <row r="5" spans="1:3" ht="35.1" customHeight="1">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -961,7 +984,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="35" customHeight="1">
+    <row r="6" spans="1:3" ht="35.1" customHeight="1">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -972,7 +995,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="35" customHeight="1">
+    <row r="7" spans="1:3" ht="35.1" customHeight="1">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -983,7 +1006,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="35" customHeight="1">
+    <row r="8" spans="1:3" ht="35.1" customHeight="1">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -994,7 +1017,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="35" customHeight="1">
+    <row r="9" spans="1:3" ht="35.1" customHeight="1">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -1005,7 +1028,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="35" customHeight="1">
+    <row r="10" spans="1:3" ht="35.1" customHeight="1">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -1013,7 +1036,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="35" customHeight="1">
+    <row r="11" spans="1:3" ht="35.1" customHeight="1">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -1024,7 +1047,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="35" customHeight="1">
+    <row r="12" spans="1:3" ht="35.1" customHeight="1">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -1035,7 +1058,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="35" customHeight="1">
+    <row r="13" spans="1:3" ht="35.1" customHeight="1">
       <c r="A13" s="1">
         <v>11</v>
       </c>
@@ -1046,7 +1069,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="35" customHeight="1">
+    <row r="14" spans="1:3" ht="35.1" customHeight="1">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -1057,7 +1080,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="35" customHeight="1">
+    <row r="15" spans="1:3" ht="35.1" customHeight="1">
       <c r="A15" s="1">
         <v>13</v>
       </c>
@@ -1068,7 +1091,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="35" customHeight="1">
+    <row r="16" spans="1:3" ht="35.1" customHeight="1">
       <c r="A16" s="1">
         <v>14</v>
       </c>
@@ -1079,7 +1102,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="35" customHeight="1">
+    <row r="17" spans="1:3" ht="35.1" customHeight="1">
       <c r="A17" s="1">
         <v>15</v>
       </c>
@@ -1087,7 +1110,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="35" customHeight="1">
+    <row r="18" spans="1:3" ht="35.1" customHeight="1">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -1098,7 +1121,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="35" customHeight="1">
+    <row r="19" spans="1:3" ht="35.1" customHeight="1">
       <c r="A19" s="1">
         <v>17</v>
       </c>
@@ -1109,7 +1132,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="35" customHeight="1">
+    <row r="20" spans="1:3" ht="35.1" customHeight="1">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -1120,7 +1143,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="35" customHeight="1">
+    <row r="21" spans="1:3" ht="35.1" customHeight="1">
       <c r="A21" s="1">
         <v>19</v>
       </c>
@@ -1128,6 +1151,17 @@
         <v>22</v>
       </c>
       <c r="C21" s="1" t="e" vm="2">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="35.1" customHeight="1">
+      <c r="A22" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C22" s="1" t="e" vm="12">
         <v>#VALUE!</v>
       </c>
     </row>

--- a/對應表.xlsx
+++ b/對應表.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\catmario\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6F8FBE5-A957-40DE-A0AE-5B22499D04ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC2F20A5-B104-45F4-ADB1-C7F1973650A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{8D3ADF05-6E10-4DC5-8529-E0F0A0AD7E8F}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="16305" xr2:uid="{8D3ADF05-6E10-4DC5-8529-E0F0A0AD7E8F}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
   <metadataTypes count="1">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="12">
+  <futureMetadata name="XLRICHVALUE" count="15">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -125,8 +125,29 @@
         </ext>
       </extLst>
     </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="12"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="13"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="14"/>
+        </ext>
+      </extLst>
+    </bk>
   </futureMetadata>
-  <valueMetadata count="12">
+  <valueMetadata count="15">
     <bk>
       <rc t="1" v="0"/>
     </bk>
@@ -162,13 +183,22 @@
     </bk>
     <bk>
       <rc t="1" v="11"/>
+    </bk>
+    <bk>
+      <rc t="1" v="12"/>
+    </bk>
+    <bk>
+      <rc t="1" v="13"/>
+    </bk>
+    <bk>
+      <rc t="1" v="14"/>
     </bk>
   </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t>編號</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -385,11 +415,19 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>u</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>stupid clode</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>brock2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>brock11</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>brock14</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -531,7 +569,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="12">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="15">
   <rv s="0">
     <v>0</v>
     <v>5</v>
@@ -578,6 +616,18 @@
   </rv>
   <rv s="0">
     <v>11</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>12</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>13</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>14</v>
     <v>5</v>
   </rv>
 </rvData>
@@ -606,6 +656,9 @@
   <rel r:id="rId10"/>
   <rel r:id="rId11"/>
   <rel r:id="rId12"/>
+  <rel r:id="rId13"/>
+  <rel r:id="rId14"/>
+  <rel r:id="rId15"/>
 </richValueRels>
 </file>
 
@@ -926,7 +979,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06C0AE9F-6DB3-40DA-B2EC-F82B368A21F6}">
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="5.625" style="1" bestFit="1" customWidth="1"/>
@@ -1155,16 +1208,55 @@
       </c>
     </row>
     <row r="22" spans="1:3" ht="35.1" customHeight="1">
-      <c r="A22" s="1" t="s">
+      <c r="A22" s="1">
+        <v>20</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="C22" s="1" t="e" vm="12">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="35.1" customHeight="1">
+      <c r="A23" s="1">
+        <v>21</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C22" s="1" t="e" vm="12">
-        <v>#VALUE!</v>
-      </c>
-    </row>
+      <c r="C23" s="1" t="e" vm="13">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="35.1" customHeight="1">
+      <c r="A24" s="1">
+        <v>22</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C24" s="1" t="e" vm="14">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="35.1" customHeight="1">
+      <c r="A25" s="1">
+        <v>23</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C25" s="1" t="e" vm="15">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="35.1" customHeight="1"/>
+    <row r="27" spans="1:3" ht="35.1" customHeight="1"/>
+    <row r="28" spans="1:3" ht="35.1" customHeight="1"/>
+    <row r="29" spans="1:3" ht="35.1" customHeight="1"/>
+    <row r="30" spans="1:3" ht="35.1" customHeight="1"/>
+    <row r="31" spans="1:3" ht="35.1" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/對應表.xlsx
+++ b/對應表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\catmario\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{162EE466-49B8-4F00-B4C5-8101D52B20F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AC00108-2BB3-49EE-A4D6-CCE6558950C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{8D3ADF05-6E10-4DC5-8529-E0F0A0AD7E8F}"/>
   </bookViews>
@@ -40,7 +40,7 @@
   <metadataTypes count="1">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="17">
+  <futureMetadata name="XLRICHVALUE" count="18">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -160,8 +160,15 @@
         </ext>
       </extLst>
     </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="17"/>
+        </ext>
+      </extLst>
+    </bk>
   </futureMetadata>
-  <valueMetadata count="17">
+  <valueMetadata count="18">
     <bk>
       <rc t="1" v="0"/>
     </bk>
@@ -212,13 +219,16 @@
     </bk>
     <bk>
       <rc t="1" v="16"/>
+    </bk>
+    <bk>
+      <rc t="1" v="17"/>
     </bk>
   </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="30">
   <si>
     <t>編號</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -453,6 +463,35 @@
   <si>
     <t>brock8</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>box(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>紅蘑菇盒</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Gen Jyuu Gothic Bold"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>flagpole</t>
   </si>
 </sst>
 </file>
@@ -593,7 +632,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="17">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="18">
   <rv s="0">
     <v>0</v>
     <v>5</v>
@@ -660,6 +699,10 @@
   </rv>
   <rv s="0">
     <v>16</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>17</v>
     <v>5</v>
   </rv>
 </rvData>
@@ -693,6 +736,7 @@
   <rel r:id="rId15"/>
   <rel r:id="rId16"/>
   <rel r:id="rId17"/>
+  <rel r:id="rId18"/>
 </richValueRels>
 </file>
 
@@ -1310,8 +1354,28 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="35.1" customHeight="1"/>
-    <row r="29" spans="1:4" ht="35.1" customHeight="1"/>
+    <row r="28" spans="1:4" ht="35.1" customHeight="1">
+      <c r="A28" s="1">
+        <v>26</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C28" s="1" t="e" vm="4">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="35.1" customHeight="1">
+      <c r="A29" s="1">
+        <v>27</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C29" s="1" t="e" vm="18">
+        <v>#VALUE!</v>
+      </c>
+    </row>
     <row r="30" spans="1:4" ht="35.1" customHeight="1"/>
     <row r="31" spans="1:4" ht="35.1" customHeight="1"/>
   </sheetData>

--- a/對應表.xlsx
+++ b/對應表.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10511"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\catmario\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/easn/code/catmario/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AE76D39-7A37-4CD8-862E-BA1A42F79882}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C10B813-4685-EF4C-933E-6BA14C1FB89B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11835" xr2:uid="{8D3ADF05-6E10-4DC5-8529-E0F0A0AD7E8F}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16620" xr2:uid="{8D3ADF05-6E10-4DC5-8529-E0F0A0AD7E8F}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -268,7 +268,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="35">
   <si>
     <t>編號</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -544,6 +544,10 @@
   </si>
   <si>
     <t>flag_back</t>
+  </si>
+  <si>
+    <t>Background2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1129,16 +1133,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06C0AE9F-6DB3-40DA-B2EC-F82B368A21F6}">
-  <dimension ref="A1:D34"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
+  <dimension ref="A1:J34"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="5.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.125" style="1" customWidth="1"/>
-    <col min="4" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.1640625" style="1" customWidth="1"/>
+    <col min="4" max="7" width="9" style="1"/>
+    <col min="8" max="8" width="16.83203125" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1146,15 +1152,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:10">
       <c r="A2" s="1">
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" ht="35.1" customHeight="1">
+      <c r="H2" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="35" customHeight="1">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -1164,151 +1173,181 @@
       <c r="C3" s="1" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" ht="35.1" customHeight="1">
+      <c r="H3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I3" s="1" t="e" vm="2">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="35" customHeight="1">
       <c r="A4" s="1">
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="1" t="e" vm="2">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="35.1" customHeight="1">
+      <c r="C4" s="1" t="e" vm="3">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I4" s="1" t="e" vm="4">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="35" customHeight="1">
       <c r="A5" s="1">
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="1" t="e" vm="3">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="35.1" customHeight="1">
+      <c r="C5" s="1" t="e" vm="5">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I5" s="1" t="e" vm="6">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="35" customHeight="1">
       <c r="A6" s="1">
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="1" t="e" vm="4">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="35.1" customHeight="1">
+      <c r="C6" s="1" t="e" vm="7">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="35" customHeight="1">
       <c r="A7" s="1">
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="1" t="e" vm="5">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="35.1" customHeight="1">
+      <c r="C7" s="1" t="e" vm="8">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="35" customHeight="1">
       <c r="A8" s="1">
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="1" t="e" vm="6">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="35.1" customHeight="1">
+      <c r="C8" s="1" t="e" vm="9">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="35" customHeight="1">
       <c r="A9" s="1">
         <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="1" t="e" vm="7">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="35.1" customHeight="1">
+      <c r="C9" s="1" t="e" vm="10">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="35" customHeight="1">
       <c r="A10" s="1">
         <v>8</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="1" t="e" vm="5">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="35.1" customHeight="1">
+      <c r="D10" s="1" t="e" vm="8">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J10" s="1" t="e" vm="11">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="35" customHeight="1">
       <c r="A11" s="1">
         <v>9</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="1" t="e" vm="8">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="35.1" customHeight="1">
+      <c r="C11" s="1" t="e" vm="12">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="35" customHeight="1">
       <c r="A12" s="1">
         <v>10</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="1" t="e" vm="4">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="35.1" customHeight="1">
+      <c r="C12" s="1" t="e" vm="7">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="35" customHeight="1">
       <c r="A13" s="1">
         <v>11</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C13" s="1" t="e" vm="3">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="35.1" customHeight="1">
+      <c r="C13" s="1" t="e" vm="5">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="35" customHeight="1">
       <c r="A14" s="1">
         <v>12</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="1" t="e" vm="4">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="35.1" customHeight="1">
+      <c r="C14" s="1" t="e" vm="7">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="35" customHeight="1">
       <c r="A15" s="1">
         <v>13</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C15" s="1" t="e" vm="9">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="35.1" customHeight="1">
+      <c r="C15" s="1" t="e" vm="13">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="35" customHeight="1">
       <c r="A16" s="1">
         <v>14</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="1" t="e" vm="10">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="35.1" customHeight="1">
+      <c r="C16" s="1" t="e" vm="14">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I16" s="1" t="e" vm="15">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="35" customHeight="1">
       <c r="A17" s="1">
         <v>15</v>
       </c>
@@ -1316,18 +1355,18 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="35.1" customHeight="1">
+    <row r="18" spans="1:3" ht="35" customHeight="1">
       <c r="A18" s="1">
         <v>16</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C18" s="1" t="e" vm="11">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="35.1" customHeight="1">
+      <c r="C18" s="1" t="e" vm="16">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="35" customHeight="1">
       <c r="A19" s="1">
         <v>17</v>
       </c>
@@ -1338,7 +1377,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="35.1" customHeight="1">
+    <row r="20" spans="1:3" ht="35" customHeight="1">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -1349,95 +1388,65 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="35.1" customHeight="1">
+    <row r="21" spans="1:3" ht="35" customHeight="1">
       <c r="A21" s="1">
         <v>19</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C21" s="1" t="e" vm="2">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="35.1" customHeight="1">
+      <c r="C21" s="1" t="e" vm="3">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="35" customHeight="1">
       <c r="A22" s="1">
         <v>20</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C22" s="1" t="e" vm="12">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" ht="35.1" customHeight="1">
+      <c r="C22" s="1" t="e" vm="17">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="35" customHeight="1">
       <c r="A23" s="1">
         <v>21</v>
       </c>
-      <c r="B23" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C23" s="1" t="e" vm="13">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" ht="35.1" customHeight="1">
+    </row>
+    <row r="24" spans="1:3" ht="35" customHeight="1">
       <c r="A24" s="1">
         <v>22</v>
       </c>
-      <c r="B24" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C24" s="1" t="e" vm="14">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="35.1" customHeight="1">
+    </row>
+    <row r="25" spans="1:3" ht="35" customHeight="1">
       <c r="A25" s="1">
         <v>23</v>
       </c>
-      <c r="B25" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C25" s="1" t="e" vm="15">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" ht="35.1" customHeight="1">
+    </row>
+    <row r="26" spans="1:3" ht="35" customHeight="1">
       <c r="A26" s="1">
         <v>24</v>
       </c>
-      <c r="B26" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C26" s="1" t="e" vm="16">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="35.1" customHeight="1">
+    </row>
+    <row r="27" spans="1:3" ht="35" customHeight="1">
       <c r="A27" s="1">
         <v>25</v>
       </c>
-      <c r="B27" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D27" s="1" t="e" vm="17">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" ht="35.1" customHeight="1">
+    </row>
+    <row r="28" spans="1:3" ht="35" customHeight="1">
       <c r="A28" s="1">
         <v>26</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C28" s="1" t="e" vm="4">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" ht="35.1" customHeight="1">
+      <c r="C28" s="1" t="e" vm="7">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="35" customHeight="1">
       <c r="A29" s="1">
         <v>27</v>
       </c>
@@ -1448,7 +1457,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="35.1" customHeight="1">
+    <row r="30" spans="1:3" ht="35" customHeight="1">
       <c r="A30" s="1">
         <v>28</v>
       </c>
@@ -1459,7 +1468,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="35.1" customHeight="1">
+    <row r="31" spans="1:3" ht="35" customHeight="1">
       <c r="A31" s="1">
         <v>29</v>
       </c>
@@ -1470,7 +1479,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="35.1" customHeight="1">
+    <row r="32" spans="1:3" ht="35" customHeight="1">
       <c r="A32" s="1">
         <v>30</v>
       </c>
@@ -1481,7 +1490,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="35.1" customHeight="1">
+    <row r="33" spans="1:3" ht="35" customHeight="1">
       <c r="A33" s="1">
         <v>31</v>
       </c>
@@ -1492,14 +1501,14 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="35.1" customHeight="1">
+    <row r="34" spans="1:3" ht="35" customHeight="1">
       <c r="A34" s="1">
         <v>32</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C34" s="1" t="e" vm="4">
+      <c r="C34" s="1" t="e" vm="7">
         <v>#VALUE!</v>
       </c>
     </row>

--- a/對應表.xlsx
+++ b/對應表.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10511"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/easn/code/catmario/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\catmario\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C10B813-4685-EF4C-933E-6BA14C1FB89B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{281A261A-A5B4-469F-887F-E7E34E927208}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16620" xr2:uid="{8D3ADF05-6E10-4DC5-8529-E0F0A0AD7E8F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{8D3ADF05-6E10-4DC5-8529-E0F0A0AD7E8F}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
   <metadataTypes count="1">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="22">
+  <futureMetadata name="XLRICHVALUE" count="26">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -195,8 +195,36 @@
         </ext>
       </extLst>
     </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="22"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="23"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="24"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="25"/>
+        </ext>
+      </extLst>
+    </bk>
   </futureMetadata>
-  <valueMetadata count="22">
+  <valueMetadata count="26">
     <bk>
       <rc t="1" v="0"/>
     </bk>
@@ -262,13 +290,25 @@
     </bk>
     <bk>
       <rc t="1" v="21"/>
+    </bk>
+    <bk>
+      <rc t="1" v="22"/>
+    </bk>
+    <bk>
+      <rc t="1" v="23"/>
+    </bk>
+    <bk>
+      <rc t="1" v="24"/>
+    </bk>
+    <bk>
+      <rc t="1" v="25"/>
     </bk>
   </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="42">
   <si>
     <t>編號</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -547,6 +587,122 @@
   </si>
   <si>
     <t>Background2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>box(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>花盒</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Gen Jyuu Gothic Bold"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>longlongtube</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>隱形</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>彈力</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Gen Jyuu Gothic Bold"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>box</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>yellowbat</t>
+  </si>
+  <si>
+    <t>greenbat</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>box(P</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>盒</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Gen Jyuu Gothic Bold"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>box(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>國王盒</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Gen Jyuu Gothic Bold"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -688,7 +844,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="22">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="26">
   <rv s="0">
     <v>0</v>
     <v>5</v>
@@ -775,6 +931,22 @@
   </rv>
   <rv s="0">
     <v>21</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>22</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>23</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>24</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>25</v>
     <v>5</v>
   </rv>
 </rvData>
@@ -813,6 +985,10 @@
   <rel r:id="rId20"/>
   <rel r:id="rId21"/>
   <rel r:id="rId22"/>
+  <rel r:id="rId23"/>
+  <rel r:id="rId24"/>
+  <rel r:id="rId25"/>
+  <rel r:id="rId26"/>
 </richValueRels>
 </file>
 
@@ -1133,14 +1309,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06C0AE9F-6DB3-40DA-B2EC-F82B368A21F6}">
-  <dimension ref="A1:J34"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
+  <dimension ref="A1:J48"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.1640625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="5.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.125" style="1" customWidth="1"/>
     <col min="4" max="7" width="9" style="1"/>
-    <col min="8" max="8" width="16.83203125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="16.875" style="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -1163,7 +1339,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="35" customHeight="1">
+    <row r="3" spans="1:10" ht="35.1" customHeight="1">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -1180,7 +1356,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="35" customHeight="1">
+    <row r="4" spans="1:10" ht="35.1" customHeight="1">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -1197,7 +1373,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="35" customHeight="1">
+    <row r="5" spans="1:10" ht="35.1" customHeight="1">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -1214,7 +1390,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="35" customHeight="1">
+    <row r="6" spans="1:10" ht="35.1" customHeight="1">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -1225,7 +1401,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="35" customHeight="1">
+    <row r="7" spans="1:10" ht="35.1" customHeight="1">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -1236,7 +1412,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="35" customHeight="1">
+    <row r="8" spans="1:10" ht="35.1" customHeight="1">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -1247,7 +1423,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="35" customHeight="1">
+    <row r="9" spans="1:10" ht="35.1" customHeight="1">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -1258,7 +1434,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="35" customHeight="1">
+    <row r="10" spans="1:10" ht="35.1" customHeight="1">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -1275,7 +1451,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="35" customHeight="1">
+    <row r="11" spans="1:10" ht="35.1" customHeight="1">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -1286,7 +1462,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="35" customHeight="1">
+    <row r="12" spans="1:10" ht="35.1" customHeight="1">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -1297,7 +1473,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="35" customHeight="1">
+    <row r="13" spans="1:10" ht="35.1" customHeight="1">
       <c r="A13" s="1">
         <v>11</v>
       </c>
@@ -1308,7 +1484,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="35" customHeight="1">
+    <row r="14" spans="1:10" ht="35.1" customHeight="1">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -1319,7 +1495,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="35" customHeight="1">
+    <row r="15" spans="1:10" ht="35.1" customHeight="1">
       <c r="A15" s="1">
         <v>13</v>
       </c>
@@ -1330,7 +1506,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="35" customHeight="1">
+    <row r="16" spans="1:10" ht="35.1" customHeight="1">
       <c r="A16" s="1">
         <v>14</v>
       </c>
@@ -1347,7 +1523,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="35" customHeight="1">
+    <row r="17" spans="1:3" ht="35.1" customHeight="1">
       <c r="A17" s="1">
         <v>15</v>
       </c>
@@ -1355,7 +1531,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="35" customHeight="1">
+    <row r="18" spans="1:3" ht="35.1" customHeight="1">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -1366,7 +1542,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="35" customHeight="1">
+    <row r="19" spans="1:3" ht="35.1" customHeight="1">
       <c r="A19" s="1">
         <v>17</v>
       </c>
@@ -1377,7 +1553,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="35" customHeight="1">
+    <row r="20" spans="1:3" ht="35.1" customHeight="1">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -1388,7 +1564,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="35" customHeight="1">
+    <row r="21" spans="1:3" ht="35.1" customHeight="1">
       <c r="A21" s="1">
         <v>19</v>
       </c>
@@ -1399,7 +1575,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="35" customHeight="1">
+    <row r="22" spans="1:3" ht="35.1" customHeight="1">
       <c r="A22" s="1">
         <v>20</v>
       </c>
@@ -1410,32 +1586,32 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="35" customHeight="1">
+    <row r="23" spans="1:3" ht="35.1" customHeight="1">
       <c r="A23" s="1">
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="35" customHeight="1">
+    <row r="24" spans="1:3" ht="35.1" customHeight="1">
       <c r="A24" s="1">
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="35" customHeight="1">
+    <row r="25" spans="1:3" ht="35.1" customHeight="1">
       <c r="A25" s="1">
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="35" customHeight="1">
+    <row r="26" spans="1:3" ht="35.1" customHeight="1">
       <c r="A26" s="1">
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="35" customHeight="1">
+    <row r="27" spans="1:3" ht="35.1" customHeight="1">
       <c r="A27" s="1">
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="35" customHeight="1">
+    <row r="28" spans="1:3" ht="35.1" customHeight="1">
       <c r="A28" s="1">
         <v>26</v>
       </c>
@@ -1446,7 +1622,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="35" customHeight="1">
+    <row r="29" spans="1:3" ht="35.1" customHeight="1">
       <c r="A29" s="1">
         <v>27</v>
       </c>
@@ -1457,7 +1633,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="35" customHeight="1">
+    <row r="30" spans="1:3" ht="35.1" customHeight="1">
       <c r="A30" s="1">
         <v>28</v>
       </c>
@@ -1468,7 +1644,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="35" customHeight="1">
+    <row r="31" spans="1:3" ht="35.1" customHeight="1">
       <c r="A31" s="1">
         <v>29</v>
       </c>
@@ -1479,7 +1655,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="35" customHeight="1">
+    <row r="32" spans="1:3" ht="35.1" customHeight="1">
       <c r="A32" s="1">
         <v>30</v>
       </c>
@@ -1490,7 +1666,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="35" customHeight="1">
+    <row r="33" spans="1:4" ht="35.1" customHeight="1">
       <c r="A33" s="1">
         <v>31</v>
       </c>
@@ -1501,7 +1677,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="35" customHeight="1">
+    <row r="34" spans="1:4" ht="35.1" customHeight="1">
       <c r="A34" s="1">
         <v>32</v>
       </c>
@@ -1512,6 +1688,90 @@
         <v>#VALUE!</v>
       </c>
     </row>
+    <row r="35" spans="1:4" ht="35.1" customHeight="1">
+      <c r="A35" s="1">
+        <v>33</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C35" s="1" t="e" vm="23">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="35.1" customHeight="1">
+      <c r="A36" s="1">
+        <v>34</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C36" s="1" t="e" vm="7">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="35.1" customHeight="1">
+      <c r="A37" s="1">
+        <v>35</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D37" s="1" t="e" vm="24">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="35.1" customHeight="1">
+      <c r="A38" s="1">
+        <v>36</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C38" s="1" t="e" vm="25">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="35.1" customHeight="1">
+      <c r="A39" s="1">
+        <v>37</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C39" s="1" t="e" vm="26">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" ht="35.1" customHeight="1">
+      <c r="A40" s="1">
+        <v>38</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C40" s="1" t="e" vm="7">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" ht="35.1" customHeight="1">
+      <c r="A41" s="1">
+        <v>39</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C41" s="1" t="e" vm="7">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="35.1" customHeight="1"/>
+    <row r="43" spans="1:4" ht="35.1" customHeight="1"/>
+    <row r="44" spans="1:4" ht="35.1" customHeight="1"/>
+    <row r="45" spans="1:4" ht="35.1" customHeight="1"/>
+    <row r="46" spans="1:4" ht="35.1" customHeight="1"/>
+    <row r="47" spans="1:4" ht="35.1" customHeight="1"/>
+    <row r="48" spans="1:4" ht="35.1" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/對應表.xlsx
+++ b/對應表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/easn/code/catmario/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C10B813-4685-EF4C-933E-6BA14C1FB89B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE603B85-9F2F-E74F-9937-44A98AED91B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16620" xr2:uid="{8D3ADF05-6E10-4DC5-8529-E0F0A0AD7E8F}"/>
   </bookViews>
@@ -268,7 +268,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="36">
   <si>
     <t>編號</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -547,6 +547,10 @@
   </si>
   <si>
     <t>Background2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>易碎隱形box</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1347,7 +1351,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="35" customHeight="1">
+    <row r="17" spans="1:4" ht="35" customHeight="1">
       <c r="A17" s="1">
         <v>15</v>
       </c>
@@ -1355,7 +1359,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="35" customHeight="1">
+    <row r="18" spans="1:4" ht="35" customHeight="1">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -1366,7 +1370,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="35" customHeight="1">
+    <row r="19" spans="1:4" ht="35" customHeight="1">
       <c r="A19" s="1">
         <v>17</v>
       </c>
@@ -1377,7 +1381,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="35" customHeight="1">
+    <row r="20" spans="1:4" ht="35" customHeight="1">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -1388,7 +1392,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="35" customHeight="1">
+    <row r="21" spans="1:4" ht="35" customHeight="1">
       <c r="A21" s="1">
         <v>19</v>
       </c>
@@ -1399,7 +1403,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="35" customHeight="1">
+    <row r="22" spans="1:4" ht="35" customHeight="1">
       <c r="A22" s="1">
         <v>20</v>
       </c>
@@ -1410,32 +1414,38 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="35" customHeight="1">
+    <row r="23" spans="1:4" ht="35" customHeight="1">
       <c r="A23" s="1">
         <v>21</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" ht="35" customHeight="1">
+      <c r="B23" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D23" s="1" t="e" vm="8">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="35" customHeight="1">
       <c r="A24" s="1">
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="35" customHeight="1">
+    <row r="25" spans="1:4" ht="35" customHeight="1">
       <c r="A25" s="1">
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="35" customHeight="1">
+    <row r="26" spans="1:4" ht="35" customHeight="1">
       <c r="A26" s="1">
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="35" customHeight="1">
+    <row r="27" spans="1:4" ht="35" customHeight="1">
       <c r="A27" s="1">
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="35" customHeight="1">
+    <row r="28" spans="1:4" ht="35" customHeight="1">
       <c r="A28" s="1">
         <v>26</v>
       </c>
@@ -1446,7 +1456,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="35" customHeight="1">
+    <row r="29" spans="1:4" ht="35" customHeight="1">
       <c r="A29" s="1">
         <v>27</v>
       </c>
@@ -1457,7 +1467,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="35" customHeight="1">
+    <row r="30" spans="1:4" ht="35" customHeight="1">
       <c r="A30" s="1">
         <v>28</v>
       </c>
@@ -1468,7 +1478,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="35" customHeight="1">
+    <row r="31" spans="1:4" ht="35" customHeight="1">
       <c r="A31" s="1">
         <v>29</v>
       </c>
@@ -1479,7 +1489,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="35" customHeight="1">
+    <row r="32" spans="1:4" ht="35" customHeight="1">
       <c r="A32" s="1">
         <v>30</v>
       </c>

--- a/對應表.xlsx
+++ b/對應表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/easn/code/catmario/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE603B85-9F2F-E74F-9937-44A98AED91B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71CCEE54-489B-A14D-B255-2949CCDF31E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16620" xr2:uid="{8D3ADF05-6E10-4DC5-8529-E0F0A0AD7E8F}"/>
   </bookViews>
@@ -268,7 +268,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="37">
   <si>
     <t>編號</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -551,6 +551,10 @@
   </si>
   <si>
     <t>易碎隱形box</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fuck box</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1380,6 +1384,9 @@
       <c r="C19" s="1" t="s">
         <v>20</v>
       </c>
+      <c r="D19" s="1" t="e" vm="8">
+        <v>#VALUE!</v>
+      </c>
     </row>
     <row r="20" spans="1:4" ht="35" customHeight="1">
       <c r="A20" s="1">
@@ -1428,6 +1435,9 @@
     <row r="24" spans="1:4" ht="35" customHeight="1">
       <c r="A24" s="1">
         <v>22</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="35" customHeight="1">

--- a/對應表.xlsx
+++ b/對應表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/easn/code/catmario/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71CCEE54-489B-A14D-B255-2949CCDF31E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12BC17BB-44CB-BF46-BFCD-A11BD8A6F8DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16620" xr2:uid="{8D3ADF05-6E10-4DC5-8529-E0F0A0AD7E8F}"/>
   </bookViews>
@@ -268,7 +268,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="40">
   <si>
     <t>編號</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -555,6 +555,18 @@
   </si>
   <si>
     <t>fuck box</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>box(紅花盒)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Background3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>box(國王盒)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1141,7 +1153,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06C0AE9F-6DB3-40DA-B2EC-F82B368A21F6}">
-  <dimension ref="A1:J34"/>
+  <dimension ref="A1:N38"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
@@ -1149,10 +1161,14 @@
     <col min="3" max="3" width="8.1640625" style="1" customWidth="1"/>
     <col min="4" max="7" width="9" style="1"/>
     <col min="8" max="8" width="16.83203125" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="1"/>
+    <col min="9" max="11" width="9" style="1"/>
+    <col min="12" max="12" width="14" style="1" customWidth="1"/>
+    <col min="13" max="13" width="17" style="1" customWidth="1"/>
+    <col min="14" max="14" width="15.33203125" style="1" customWidth="1"/>
+    <col min="15" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1160,7 +1176,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:12">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -1170,8 +1186,11 @@
       <c r="H2" s="1" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" ht="35" customHeight="1">
+      <c r="L2" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="35" customHeight="1">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -1188,7 +1207,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="35" customHeight="1">
+    <row r="4" spans="1:12" ht="35" customHeight="1">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -1205,7 +1224,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="35" customHeight="1">
+    <row r="5" spans="1:12" ht="35" customHeight="1">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -1222,7 +1241,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="35" customHeight="1">
+    <row r="6" spans="1:12" ht="35" customHeight="1">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -1233,7 +1252,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="35" customHeight="1">
+    <row r="7" spans="1:12" ht="35" customHeight="1">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -1244,7 +1263,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="35" customHeight="1">
+    <row r="8" spans="1:12" ht="35" customHeight="1">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -1255,7 +1274,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="35" customHeight="1">
+    <row r="9" spans="1:12" ht="35" customHeight="1">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -1266,7 +1285,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="35" customHeight="1">
+    <row r="10" spans="1:12" ht="35" customHeight="1">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -1283,7 +1302,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="35" customHeight="1">
+    <row r="11" spans="1:12" ht="35" customHeight="1">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -1294,7 +1313,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="35" customHeight="1">
+    <row r="12" spans="1:12" ht="35" customHeight="1">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -1305,7 +1324,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="35" customHeight="1">
+    <row r="13" spans="1:12" ht="35" customHeight="1">
       <c r="A13" s="1">
         <v>11</v>
       </c>
@@ -1316,7 +1335,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="35" customHeight="1">
+    <row r="14" spans="1:12" ht="35" customHeight="1">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -1327,7 +1346,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="35" customHeight="1">
+    <row r="15" spans="1:12" ht="35" customHeight="1">
       <c r="A15" s="1">
         <v>13</v>
       </c>
@@ -1338,7 +1357,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="35" customHeight="1">
+    <row r="16" spans="1:12" ht="35" customHeight="1">
       <c r="A16" s="1">
         <v>14</v>
       </c>
@@ -1355,15 +1374,18 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="35" customHeight="1">
+    <row r="17" spans="1:14" ht="35" customHeight="1">
       <c r="A17" s="1">
         <v>15</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" ht="35" customHeight="1">
+      <c r="D17" s="1" t="e" vm="8">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="35" customHeight="1">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -1374,7 +1396,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="35" customHeight="1">
+    <row r="19" spans="1:14" ht="35" customHeight="1">
       <c r="A19" s="1">
         <v>17</v>
       </c>
@@ -1388,7 +1410,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="35" customHeight="1">
+    <row r="20" spans="1:14" ht="35" customHeight="1">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -1399,7 +1421,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="35" customHeight="1">
+    <row r="21" spans="1:14" ht="35" customHeight="1">
       <c r="A21" s="1">
         <v>19</v>
       </c>
@@ -1410,7 +1432,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="35" customHeight="1">
+    <row r="22" spans="1:14" ht="35" customHeight="1">
       <c r="A22" s="1">
         <v>20</v>
       </c>
@@ -1421,7 +1443,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="35" customHeight="1">
+    <row r="23" spans="1:14" ht="35" customHeight="1">
       <c r="A23" s="1">
         <v>21</v>
       </c>
@@ -1431,8 +1453,14 @@
       <c r="D23" s="1" t="e" vm="8">
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" ht="35" customHeight="1">
+      <c r="L23" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="N23" s="1" t="e" vm="8">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" ht="35" customHeight="1">
       <c r="A24" s="1">
         <v>22</v>
       </c>
@@ -1440,22 +1468,22 @@
         <v>36</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="35" customHeight="1">
+    <row r="25" spans="1:14" ht="35" customHeight="1">
       <c r="A25" s="1">
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="35" customHeight="1">
+    <row r="26" spans="1:14" ht="35" customHeight="1">
       <c r="A26" s="1">
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="35" customHeight="1">
+    <row r="27" spans="1:14" ht="35" customHeight="1">
       <c r="A27" s="1">
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="35" customHeight="1">
+    <row r="28" spans="1:14" ht="35" customHeight="1">
       <c r="A28" s="1">
         <v>26</v>
       </c>
@@ -1466,7 +1494,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="35" customHeight="1">
+    <row r="29" spans="1:14" ht="35" customHeight="1">
       <c r="A29" s="1">
         <v>27</v>
       </c>
@@ -1477,7 +1505,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="35" customHeight="1">
+    <row r="30" spans="1:14" ht="35" customHeight="1">
       <c r="A30" s="1">
         <v>28</v>
       </c>
@@ -1488,7 +1516,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="35" customHeight="1">
+    <row r="31" spans="1:14" ht="35" customHeight="1">
       <c r="A31" s="1">
         <v>29</v>
       </c>
@@ -1499,7 +1527,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="35" customHeight="1">
+    <row r="32" spans="1:14" ht="35" customHeight="1">
       <c r="A32" s="1">
         <v>30</v>
       </c>
@@ -1532,6 +1560,30 @@
         <v>#VALUE!</v>
       </c>
     </row>
+    <row r="35" spans="1:3" ht="37" customHeight="1">
+      <c r="A35" s="1">
+        <v>34</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C35" s="1" t="e" vm="7">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="38" customHeight="1">
+      <c r="A36" s="1">
+        <v>39</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C36" s="1" t="e" vm="7">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="47" customHeight="1"/>
+    <row r="38" spans="1:3" ht="47" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/對應表.xlsx
+++ b/對應表.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10511"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/easn/code/catmario/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\catmario\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12BC17BB-44CB-BF46-BFCD-A11BD8A6F8DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19006122-5CDE-4B40-AE59-BACB2AACA764}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16620" xr2:uid="{8D3ADF05-6E10-4DC5-8529-E0F0A0AD7E8F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{8D3ADF05-6E10-4DC5-8529-E0F0A0AD7E8F}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
   <metadataTypes count="1">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="22">
+  <futureMetadata name="XLRICHVALUE" count="23">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -195,8 +195,15 @@
         </ext>
       </extLst>
     </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="22"/>
+        </ext>
+      </extLst>
+    </bk>
   </futureMetadata>
-  <valueMetadata count="22">
+  <valueMetadata count="23">
     <bk>
       <rc t="1" v="0"/>
     </bk>
@@ -262,13 +269,16 @@
     </bk>
     <bk>
       <rc t="1" v="21"/>
+    </bk>
+    <bk>
+      <rc t="1" v="22"/>
     </bk>
   </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="41">
   <si>
     <t>編號</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -568,6 +578,9 @@
   <si>
     <t>box(國王盒)</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>platform</t>
   </si>
 </sst>
 </file>
@@ -708,7 +721,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="22">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="23">
   <rv s="0">
     <v>0</v>
     <v>5</v>
@@ -795,6 +808,10 @@
   </rv>
   <rv s="0">
     <v>21</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>22</v>
     <v>5</v>
   </rv>
 </rvData>
@@ -833,6 +850,7 @@
   <rel r:id="rId20"/>
   <rel r:id="rId21"/>
   <rel r:id="rId22"/>
+  <rel r:id="rId23"/>
 </richValueRels>
 </file>
 
@@ -1154,17 +1172,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06C0AE9F-6DB3-40DA-B2EC-F82B368A21F6}">
   <dimension ref="A1:N38"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.1640625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="5.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.125" style="1" customWidth="1"/>
     <col min="4" max="7" width="9" style="1"/>
-    <col min="8" max="8" width="16.83203125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="16.875" style="1" customWidth="1"/>
     <col min="9" max="11" width="9" style="1"/>
     <col min="12" max="12" width="14" style="1" customWidth="1"/>
     <col min="13" max="13" width="17" style="1" customWidth="1"/>
-    <col min="14" max="14" width="15.33203125" style="1" customWidth="1"/>
+    <col min="14" max="14" width="15.375" style="1" customWidth="1"/>
     <col min="15" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -1190,7 +1208,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="35" customHeight="1">
+    <row r="3" spans="1:12" ht="35.1" customHeight="1">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -1207,7 +1225,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="35" customHeight="1">
+    <row r="4" spans="1:12" ht="35.1" customHeight="1">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -1224,7 +1242,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="35" customHeight="1">
+    <row r="5" spans="1:12" ht="35.1" customHeight="1">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -1241,7 +1259,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="35" customHeight="1">
+    <row r="6" spans="1:12" ht="35.1" customHeight="1">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -1252,7 +1270,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="35" customHeight="1">
+    <row r="7" spans="1:12" ht="35.1" customHeight="1">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -1263,7 +1281,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="35" customHeight="1">
+    <row r="8" spans="1:12" ht="35.1" customHeight="1">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -1274,7 +1292,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="35" customHeight="1">
+    <row r="9" spans="1:12" ht="35.1" customHeight="1">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -1285,7 +1303,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="35" customHeight="1">
+    <row r="10" spans="1:12" ht="35.1" customHeight="1">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -1302,7 +1320,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="35" customHeight="1">
+    <row r="11" spans="1:12" ht="35.1" customHeight="1">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -1313,7 +1331,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="35" customHeight="1">
+    <row r="12" spans="1:12" ht="35.1" customHeight="1">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -1324,7 +1342,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="35" customHeight="1">
+    <row r="13" spans="1:12" ht="35.1" customHeight="1">
       <c r="A13" s="1">
         <v>11</v>
       </c>
@@ -1335,7 +1353,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="35" customHeight="1">
+    <row r="14" spans="1:12" ht="35.1" customHeight="1">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -1346,7 +1364,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="35" customHeight="1">
+    <row r="15" spans="1:12" ht="35.1" customHeight="1">
       <c r="A15" s="1">
         <v>13</v>
       </c>
@@ -1357,7 +1375,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="35" customHeight="1">
+    <row r="16" spans="1:12" ht="35.1" customHeight="1">
       <c r="A16" s="1">
         <v>14</v>
       </c>
@@ -1374,7 +1392,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="35" customHeight="1">
+    <row r="17" spans="1:14" ht="35.1" customHeight="1">
       <c r="A17" s="1">
         <v>15</v>
       </c>
@@ -1385,7 +1403,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="35" customHeight="1">
+    <row r="18" spans="1:14" ht="35.1" customHeight="1">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -1396,7 +1414,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="35" customHeight="1">
+    <row r="19" spans="1:14" ht="35.1" customHeight="1">
       <c r="A19" s="1">
         <v>17</v>
       </c>
@@ -1410,7 +1428,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="35" customHeight="1">
+    <row r="20" spans="1:14" ht="35.1" customHeight="1">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -1421,7 +1439,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="35" customHeight="1">
+    <row r="21" spans="1:14" ht="35.1" customHeight="1">
       <c r="A21" s="1">
         <v>19</v>
       </c>
@@ -1432,7 +1450,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="35" customHeight="1">
+    <row r="22" spans="1:14" ht="35.1" customHeight="1">
       <c r="A22" s="1">
         <v>20</v>
       </c>
@@ -1443,7 +1461,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="35" customHeight="1">
+    <row r="23" spans="1:14" ht="35.1" customHeight="1">
       <c r="A23" s="1">
         <v>21</v>
       </c>
@@ -1460,7 +1478,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="35" customHeight="1">
+    <row r="24" spans="1:14" ht="35.1" customHeight="1">
       <c r="A24" s="1">
         <v>22</v>
       </c>
@@ -1468,22 +1486,22 @@
         <v>36</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="35" customHeight="1">
+    <row r="25" spans="1:14" ht="35.1" customHeight="1">
       <c r="A25" s="1">
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="35" customHeight="1">
+    <row r="26" spans="1:14" ht="35.1" customHeight="1">
       <c r="A26" s="1">
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:14" ht="35" customHeight="1">
+    <row r="27" spans="1:14" ht="35.1" customHeight="1">
       <c r="A27" s="1">
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:14" ht="35" customHeight="1">
+    <row r="28" spans="1:14" ht="35.1" customHeight="1">
       <c r="A28" s="1">
         <v>26</v>
       </c>
@@ -1494,7 +1512,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="29" spans="1:14" ht="35" customHeight="1">
+    <row r="29" spans="1:14" ht="35.1" customHeight="1">
       <c r="A29" s="1">
         <v>27</v>
       </c>
@@ -1505,7 +1523,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="30" spans="1:14" ht="35" customHeight="1">
+    <row r="30" spans="1:14" ht="35.1" customHeight="1">
       <c r="A30" s="1">
         <v>28</v>
       </c>
@@ -1516,7 +1534,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="31" spans="1:14" ht="35" customHeight="1">
+    <row r="31" spans="1:14" ht="35.1" customHeight="1">
       <c r="A31" s="1">
         <v>29</v>
       </c>
@@ -1527,7 +1545,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="32" spans="1:14" ht="35" customHeight="1">
+    <row r="32" spans="1:14" ht="35.1" customHeight="1">
       <c r="A32" s="1">
         <v>30</v>
       </c>
@@ -1538,7 +1556,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="35" customHeight="1">
+    <row r="33" spans="1:3" ht="35.1" customHeight="1">
       <c r="A33" s="1">
         <v>31</v>
       </c>
@@ -1549,7 +1567,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="35" customHeight="1">
+    <row r="34" spans="1:3" ht="35.1" customHeight="1">
       <c r="A34" s="1">
         <v>32</v>
       </c>
@@ -1560,7 +1578,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="37" customHeight="1">
+    <row r="35" spans="1:3" ht="36.950000000000003" customHeight="1">
       <c r="A35" s="1">
         <v>34</v>
       </c>
@@ -1571,7 +1589,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="38" customHeight="1">
+    <row r="36" spans="1:3" ht="38.1" customHeight="1">
       <c r="A36" s="1">
         <v>39</v>
       </c>
@@ -1582,8 +1600,18 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="47" customHeight="1"/>
-    <row r="38" spans="1:3" ht="47" customHeight="1"/>
+    <row r="37" spans="1:3" ht="47.1" customHeight="1">
+      <c r="A37" s="1">
+        <v>40</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C37" s="1" t="e" vm="23">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="47.1" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/對應表.xlsx
+++ b/對應表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/easn/code/catmario/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C18CEDB8-8F17-F14B-AFF6-94739F7CD7ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2C69C78-3991-C543-AFDE-C96EF6D63300}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16620" xr2:uid="{8D3ADF05-6E10-4DC5-8529-E0F0A0AD7E8F}"/>
   </bookViews>

--- a/對應表.xlsx
+++ b/對應表.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10511"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/easn/code/catmario/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\catmario\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2C69C78-3991-C543-AFDE-C96EF6D63300}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C86B2DBC-24BD-43DD-83D4-6C7D4F6A7555}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16620" xr2:uid="{8D3ADF05-6E10-4DC5-8529-E0F0A0AD7E8F}"/>
+    <workbookView xWindow="1440" yWindow="2550" windowWidth="21600" windowHeight="11835" xr2:uid="{8D3ADF05-6E10-4DC5-8529-E0F0A0AD7E8F}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -1158,17 +1158,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06C0AE9F-6DB3-40DA-B2EC-F82B368A21F6}">
   <dimension ref="A1:N38"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.1640625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="5.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.125" style="1" customWidth="1"/>
     <col min="4" max="7" width="9" style="1"/>
-    <col min="8" max="8" width="16.83203125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="16.875" style="1" customWidth="1"/>
     <col min="9" max="11" width="9" style="1"/>
     <col min="12" max="12" width="14" style="1" customWidth="1"/>
     <col min="13" max="13" width="17" style="1" customWidth="1"/>
-    <col min="14" max="14" width="15.33203125" style="1" customWidth="1"/>
+    <col min="14" max="14" width="15.375" style="1" customWidth="1"/>
     <col min="15" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -1194,7 +1194,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="35" customHeight="1">
+    <row r="3" spans="1:12" ht="35.1" customHeight="1">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -1211,7 +1211,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="35" customHeight="1">
+    <row r="4" spans="1:12" ht="35.1" customHeight="1">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -1228,7 +1228,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="35" customHeight="1">
+    <row r="5" spans="1:12" ht="35.1" customHeight="1">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -1245,7 +1245,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="35" customHeight="1">
+    <row r="6" spans="1:12" ht="35.1" customHeight="1">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -1256,7 +1256,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="35" customHeight="1">
+    <row r="7" spans="1:12" ht="35.1" customHeight="1">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -1267,7 +1267,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="35" customHeight="1">
+    <row r="8" spans="1:12" ht="35.1" customHeight="1">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -1278,7 +1278,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="35" customHeight="1">
+    <row r="9" spans="1:12" ht="35.1" customHeight="1">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -1289,7 +1289,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="35" customHeight="1">
+    <row r="10" spans="1:12" ht="35.1" customHeight="1">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -1306,7 +1306,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="35" customHeight="1">
+    <row r="11" spans="1:12" ht="35.1" customHeight="1">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -1317,7 +1317,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="35" customHeight="1">
+    <row r="12" spans="1:12" ht="35.1" customHeight="1">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -1328,7 +1328,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="35" customHeight="1">
+    <row r="13" spans="1:12" ht="35.1" customHeight="1">
       <c r="A13" s="1">
         <v>11</v>
       </c>
@@ -1339,7 +1339,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="35" customHeight="1">
+    <row r="14" spans="1:12" ht="35.1" customHeight="1">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -1350,7 +1350,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="35" customHeight="1">
+    <row r="15" spans="1:12" ht="35.1" customHeight="1">
       <c r="A15" s="1">
         <v>13</v>
       </c>
@@ -1361,7 +1361,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="35" customHeight="1">
+    <row r="16" spans="1:12" ht="35.1" customHeight="1">
       <c r="A16" s="1">
         <v>14</v>
       </c>
@@ -1378,7 +1378,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="35" customHeight="1">
+    <row r="17" spans="1:14" ht="35.1" customHeight="1">
       <c r="A17" s="1">
         <v>15</v>
       </c>
@@ -1389,7 +1389,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="35" customHeight="1">
+    <row r="18" spans="1:14" ht="35.1" customHeight="1">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -1400,7 +1400,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="35" customHeight="1">
+    <row r="19" spans="1:14" ht="35.1" customHeight="1">
       <c r="A19" s="1">
         <v>17</v>
       </c>
@@ -1414,7 +1414,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="35" customHeight="1">
+    <row r="20" spans="1:14" ht="35.1" customHeight="1">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -1425,7 +1425,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="35" customHeight="1">
+    <row r="21" spans="1:14" ht="35.1" customHeight="1">
       <c r="A21" s="1">
         <v>19</v>
       </c>
@@ -1436,7 +1436,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="35" customHeight="1">
+    <row r="22" spans="1:14" ht="35.1" customHeight="1">
       <c r="A22" s="1">
         <v>20</v>
       </c>
@@ -1447,7 +1447,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="35" customHeight="1">
+    <row r="23" spans="1:14" ht="35.1" customHeight="1">
       <c r="A23" s="1">
         <v>21</v>
       </c>
@@ -1464,7 +1464,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="35" customHeight="1">
+    <row r="24" spans="1:14" ht="35.1" customHeight="1">
       <c r="A24" s="1">
         <v>22</v>
       </c>
@@ -1472,22 +1472,22 @@
         <v>36</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="35" customHeight="1">
+    <row r="25" spans="1:14" ht="35.1" customHeight="1">
       <c r="A25" s="1">
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="35" customHeight="1">
+    <row r="26" spans="1:14" ht="35.1" customHeight="1">
       <c r="A26" s="1">
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:14" ht="35" customHeight="1">
+    <row r="27" spans="1:14" ht="35.1" customHeight="1">
       <c r="A27" s="1">
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:14" ht="35" customHeight="1">
+    <row r="28" spans="1:14" ht="35.1" customHeight="1">
       <c r="A28" s="1">
         <v>26</v>
       </c>
@@ -1498,7 +1498,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="29" spans="1:14" ht="35" customHeight="1">
+    <row r="29" spans="1:14" ht="35.1" customHeight="1">
       <c r="A29" s="1">
         <v>27</v>
       </c>
@@ -1509,7 +1509,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="30" spans="1:14" ht="35" customHeight="1">
+    <row r="30" spans="1:14" ht="35.1" customHeight="1">
       <c r="A30" s="1">
         <v>28</v>
       </c>
@@ -1520,7 +1520,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="31" spans="1:14" ht="35" customHeight="1">
+    <row r="31" spans="1:14" ht="35.1" customHeight="1">
       <c r="A31" s="1">
         <v>29</v>
       </c>
@@ -1531,7 +1531,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="32" spans="1:14" ht="35" customHeight="1">
+    <row r="32" spans="1:14" ht="35.1" customHeight="1">
       <c r="A32" s="1">
         <v>30</v>
       </c>
@@ -1542,7 +1542,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="35" customHeight="1">
+    <row r="33" spans="1:3" ht="35.1" customHeight="1">
       <c r="A33" s="1">
         <v>31</v>
       </c>
@@ -1553,7 +1553,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="35" customHeight="1">
+    <row r="34" spans="1:3" ht="35.1" customHeight="1">
       <c r="A34" s="1">
         <v>32</v>
       </c>
@@ -1564,7 +1564,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="37" customHeight="1">
+    <row r="35" spans="1:3" ht="36.950000000000003" customHeight="1">
       <c r="A35" s="1">
         <v>34</v>
       </c>
@@ -1575,7 +1575,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="38" customHeight="1">
+    <row r="36" spans="1:3" ht="38.1" customHeight="1">
       <c r="A36" s="1">
         <v>39</v>
       </c>
@@ -1586,7 +1586,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="47" customHeight="1">
+    <row r="37" spans="1:3" ht="47.1" customHeight="1">
       <c r="A37" s="1">
         <v>40</v>
       </c>
@@ -1594,7 +1594,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="47" customHeight="1"/>
+    <row r="38" spans="1:3" ht="47.1" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
